--- a/app/reports/HON_research.xlsx
+++ b/app/reports/HON_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.736</v>
+        <v>0.742</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>273.85</v>
+        <v>271.17</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>227.845</v>
+        <v>224.23</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.202</v>
+        <v>0.209</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.497</v>
+        <v>0.513</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.702</v>
+        <v>0.709</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04480999946594239</v>
+        <v>0.04525000095367432</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>316826557.282363</v>
+        <v>316826540.7483388</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>227.845</v>
+        <v>224.23</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>72187346944</v>
+        <v>71042015232</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.18</v>
+        <v>17.9</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.64</v>
+        <v>11.69</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>96799653888</v>
+        <v>98678398976</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.610645</v>
+        <v>23.006525</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.46</v>
+        <v>15.284</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.538</v>
+        <v>4.486</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>169976905728</v>
+        <v>160483213312</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>35.696712</v>
+        <v>33.66478</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>24.071</v>
+        <v>24.509</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>160554287104</v>
+        <v>152454348800</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>40.53726</v>
+        <v>38.454456</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>27.727</v>
+        <v>28.639</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>6.166</v>
+        <v>6.369</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>101707440128</v>
+        <v>101148999680</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.683563</v>
+        <v>23.5239</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.501</v>
+        <v>16.64</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.989</v>
+        <v>2.006</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>124166569984</v>
+        <v>123146330112</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>26.091812</v>
+        <v>25.852371</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>18.095</v>
+        <v>17.867</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>1.926</v>
+        <v>1.902</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>82548449280</v>
+        <v>81823473664</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>30.554056</v>
+        <v>30.227362</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>14.589</v>
+        <v>14.481</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.638</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>77602119680</v>
+        <v>77437362176</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.12743</v>
+        <v>17.10179</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.791</v>
+        <v>12.766</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.206</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>121925541888</v>
+        <v>120024784896</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.735405</v>
+        <v>35.12638</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>23.822</v>
+        <v>24.017</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.219</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HON_research.xlsx
+++ b/app/reports/HON_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>271.17</v>
+        <v>268.05</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>224.23</v>
+        <v>221.79</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.513</v>
+        <v>0.524</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04525000095367432</v>
+        <v>0.04577000141143799</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>316826540.7483388</v>
+        <v>316826551.0978854</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>224.23</v>
+        <v>221.79</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>71042015232</v>
+        <v>70268960768</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>17.9</v>
+        <v>17.73</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.69</v>
+        <v>11.46</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>98678398976</v>
+        <v>96559808512</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>23.006525</v>
+        <v>22.55462</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>15.284</v>
+        <v>15.67</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.486</v>
+        <v>4.599</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>160483213312</v>
+        <v>160418430976</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>33.66478</v>
+        <v>33.708454</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>24.509</v>
+        <v>23.518</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>152454348800</v>
+        <v>154211401728</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>38.454456</v>
+        <v>38.897648</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>28.639</v>
+        <v>27.553</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>6.369</v>
+        <v>6.127</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>101148999680</v>
+        <v>100547289088</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.5239</v>
+        <v>23.413412</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.64</v>
+        <v>16.547</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.006</v>
+        <v>1.995</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>123146330112</v>
+        <v>121839108096</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>25.852371</v>
+        <v>25.565569</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>17.867</v>
+        <v>17.791</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>1.902</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>81823473664</v>
+        <v>80884654080</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>30.227362</v>
+        <v>29.938225</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>14.481</v>
+        <v>14.386</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.611</v>
+        <v>3.587</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>77437362176</v>
+        <v>76953731072</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.10179</v>
+        <v>16.984325</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.766</v>
+        <v>12.791</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.202</v>
+        <v>2.206</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>120024784896</v>
+        <v>117915992064</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.12638</v>
+        <v>34.509224</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>24.017</v>
+        <v>23.698</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.27</v>
+        <v>6.187</v>
       </c>
     </row>
     <row r="15">
